--- a/artfynd/A 44376-2024 artfynd.xlsx
+++ b/artfynd/A 44376-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119822960</v>
+        <v>119822970</v>
       </c>
       <c r="B2" t="n">
-        <v>79607</v>
+        <v>82321</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>622715</v>
+        <v>622930</v>
       </c>
       <c r="R2" t="n">
-        <v>7049566</v>
+        <v>7049464</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119822959</v>
+        <v>119822958</v>
       </c>
       <c r="B3" t="n">
-        <v>79636</v>
+        <v>91023</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>1209</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>622715</v>
+        <v>622642</v>
       </c>
       <c r="R3" t="n">
-        <v>7049566</v>
+        <v>7049511</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119822965</v>
+        <v>119822960</v>
       </c>
       <c r="B4" t="n">
-        <v>90562</v>
+        <v>79623</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>622823</v>
+        <v>622715</v>
       </c>
       <c r="R4" t="n">
-        <v>7049508</v>
+        <v>7049566</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119822968</v>
+        <v>119822959</v>
       </c>
       <c r="B5" t="n">
-        <v>57421</v>
+        <v>79652</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,38 +997,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103031</v>
+        <v>6462</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kebbeberget, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>622930</v>
+        <v>622715</v>
       </c>
       <c r="R5" t="n">
-        <v>7049464</v>
+        <v>7049566</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1087,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119822958</v>
+        <v>119822965</v>
       </c>
       <c r="B6" t="n">
-        <v>91005</v>
+        <v>90580</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1127,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>622642</v>
+        <v>622823</v>
       </c>
       <c r="R6" t="n">
-        <v>7049511</v>
+        <v>7049508</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1189,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119822970</v>
+        <v>119822968</v>
       </c>
       <c r="B7" t="n">
-        <v>82305</v>
+        <v>57431</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,28 +1197,32 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1312</v>
+        <v>103031</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kebbeberget, Ång</t>

--- a/artfynd/A 44376-2024 artfynd.xlsx
+++ b/artfynd/A 44376-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119822970</v>
+        <v>119822960</v>
       </c>
       <c r="B2" t="n">
-        <v>82321</v>
+        <v>79623</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>622930</v>
+        <v>622715</v>
       </c>
       <c r="R2" t="n">
-        <v>7049464</v>
+        <v>7049566</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119822958</v>
+        <v>119822965</v>
       </c>
       <c r="B3" t="n">
-        <v>91023</v>
+        <v>90580</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>622642</v>
+        <v>622823</v>
       </c>
       <c r="R3" t="n">
-        <v>7049511</v>
+        <v>7049508</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119822960</v>
+        <v>119822968</v>
       </c>
       <c r="B4" t="n">
-        <v>79623</v>
+        <v>57431</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,38 +891,42 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>103031</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kebbeberget, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>622715</v>
+        <v>622930</v>
       </c>
       <c r="R4" t="n">
-        <v>7049566</v>
+        <v>7049464</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1083,10 +1087,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119822965</v>
+        <v>119822958</v>
       </c>
       <c r="B6" t="n">
-        <v>90580</v>
+        <v>91023</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1099,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1127,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>622823</v>
+        <v>622642</v>
       </c>
       <c r="R6" t="n">
-        <v>7049508</v>
+        <v>7049511</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1189,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119822968</v>
+        <v>119822970</v>
       </c>
       <c r="B7" t="n">
-        <v>57431</v>
+        <v>82321</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,32 +1201,28 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103031</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kebbeberget, Ång</t>

--- a/artfynd/A 44376-2024 artfynd.xlsx
+++ b/artfynd/A 44376-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119822960</v>
+        <v>119822959</v>
       </c>
       <c r="B2" t="n">
-        <v>79623</v>
+        <v>79652</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119822965</v>
+        <v>119822960</v>
       </c>
       <c r="B3" t="n">
-        <v>90580</v>
+        <v>79623</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>622823</v>
+        <v>622715</v>
       </c>
       <c r="R3" t="n">
-        <v>7049508</v>
+        <v>7049566</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119822968</v>
+        <v>119822970</v>
       </c>
       <c r="B4" t="n">
-        <v>57431</v>
+        <v>82321</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,32 +891,28 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103031</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kebbeberget, Ång</t>
@@ -985,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119822959</v>
+        <v>119822965</v>
       </c>
       <c r="B5" t="n">
-        <v>79652</v>
+        <v>90580</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1025,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>622715</v>
+        <v>622823</v>
       </c>
       <c r="R5" t="n">
-        <v>7049566</v>
+        <v>7049508</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1087,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119822958</v>
+        <v>119822968</v>
       </c>
       <c r="B6" t="n">
-        <v>91023</v>
+        <v>57431</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,38 +1095,42 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1209</v>
+        <v>103031</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Kebbeberget, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>622642</v>
+        <v>622930</v>
       </c>
       <c r="R6" t="n">
-        <v>7049511</v>
+        <v>7049464</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1189,10 +1189,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119822970</v>
+        <v>119822958</v>
       </c>
       <c r="B7" t="n">
-        <v>82321</v>
+        <v>91023</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,25 +1201,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1312</v>
+        <v>1209</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1229,10 +1229,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>622930</v>
+        <v>622642</v>
       </c>
       <c r="R7" t="n">
-        <v>7049464</v>
+        <v>7049511</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 44376-2024 artfynd.xlsx
+++ b/artfynd/A 44376-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119822965</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119822958</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119822970</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119822960</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119822959</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119822957</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1355,8 +1390,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119822968</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>